--- a/data/trans_dic/P21D_2_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21D_2_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 9,2</t>
+          <t>2,43; 9,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,86</t>
+          <t>1,94; 7,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,48</t>
+          <t>2,81; 7,57</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,69</t>
+          <t>1,19; 6,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,22</t>
+          <t>0,79; 5,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,62</t>
+          <t>1,42; 4,4</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,15</t>
+          <t>0,0; 6,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,73</t>
+          <t>1,44; 6,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,05</t>
+          <t>1,3; 5,18</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,55; 9,18</t>
+          <t>2,55; 9,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 8,45</t>
+          <t>1,95; 8,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,42</t>
+          <t>2,85; 7,43</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,55</t>
+          <t>0,99; 3,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,18</t>
+          <t>0,59; 2,14</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,32</t>
+          <t>0,84; 9,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,67</t>
+          <t>0,39; 3,46</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,26</t>
+          <t>0,87; 2,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,58</t>
+          <t>1,65; 3,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,53</t>
+          <t>1,37; 2,59</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3294; 14198</t>
+          <t>3742; 15055</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2505; 9926</t>
+          <t>2453; 9252</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7417; 20980</t>
+          <t>7897; 21229</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3038; 14127</t>
+          <t>2524; 13821</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2132; 12396</t>
+          <t>1867; 12024</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6195; 20717</t>
+          <t>6368; 19731</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5842</t>
+          <t>0; 5997</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1992; 9794</t>
+          <t>2092; 9507</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3095; 12137</t>
+          <t>3132; 12451</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2054</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4816</t>
+          <t>0; 5004</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4523</t>
+          <t>0; 3982</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1243</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 835</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1002</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3208; 11528</t>
+          <t>3198; 11837</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2171; 9380</t>
+          <t>2159; 9624</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6541; 17549</t>
+          <t>6741; 17565</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5033</t>
+          <t>0; 5145</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2607; 10840</t>
+          <t>3026; 11850</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3742; 13424</t>
+          <t>3669; 13184</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6965</t>
+          <t>0; 6605</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2783; 29030</t>
+          <t>2918; 33364</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2924; 33143</t>
+          <t>3529; 31239</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>15063; 37634</t>
+          <t>14538; 37524</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>25945; 56964</t>
+          <t>26281; 59403</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45105; 82350</t>
+          <t>44458; 84305</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_2_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21D_2_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 9,76</t>
+          <t>4,78; 15,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 7,32</t>
+          <t>4,43; 14,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,57</t>
+          <t>5,35; 11,93</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,54</t>
+          <t>1,47; 7,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,07</t>
+          <t>1,02; 5,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,4</t>
+          <t>1,72; 5,15</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,32</t>
+          <t>0,0; 5,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,53</t>
+          <t>1,32; 6,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,18</t>
+          <t>1,34; 4,89</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,55; 9,42</t>
+          <t>3,04; 10,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,95; 8,67</t>
+          <t>1,94; 8,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,43</t>
+          <t>2,96; 7,67</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,88</t>
+          <t>1,01; 3,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,14</t>
+          <t>0,64; 2,2</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 9,56</t>
+          <t>0,55; 2,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,46</t>
+          <t>0,4; 1,83</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,26</t>
+          <t>1,54; 3,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,73</t>
+          <t>1,81; 3,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,59</t>
+          <t>1,85; 2,82</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>24290</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3742; 15055</t>
+          <t>7375; 23270</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2453; 9252</t>
+          <t>6146; 20258</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7897; 21229</t>
+          <t>15669; 34953</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12061</t>
+          <t>14034</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2524; 13821</t>
+          <t>3264; 16478</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1867; 12024</t>
+          <t>2584; 13626</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6368; 19731</t>
+          <t>8155; 24417</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>6401</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5997</t>
+          <t>0; 5513</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2092; 9507</t>
+          <t>1928; 9262</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3132; 12451</t>
+          <t>3217; 11696</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1292</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5004</t>
+          <t>0; 4290</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3982</t>
+          <t>0; 4847</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>12307</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3198; 11837</t>
+          <t>3853; 13004</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2159; 9624</t>
+          <t>2207; 10098</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6741; 17565</t>
+          <t>7116; 18453</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>8436</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5145</t>
+          <t>0; 5948</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3026; 11850</t>
+          <t>3577; 13106</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3669; 13184</t>
+          <t>4538; 15541</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>7338</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6605</t>
+          <t>0; 6609</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2918; 33364</t>
+          <t>2250; 10889</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3529; 31239</t>
+          <t>3109; 14052</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>74096</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>14538; 37524</t>
+          <t>24192; 48147</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>26281; 59403</t>
+          <t>30641; 54152</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44458; 84305</t>
+          <t>60451; 91886</t>
         </is>
       </c>
     </row>
